--- a/docs/beispiele/import-testdatei-ap27.xlsx
+++ b/docs/beispiele/import-testdatei-ap27.xlsx
@@ -3615,7 +3615,7 @@
       </c>
       <c r="D16" s="24" t="inlineStr">
         <is>
-          <t>Nacharbeit; 'Meinten Sie …?' mit PLZ zu Mosbach (lokal)</t>
+          <t>PLZ aus Ort ergänzt (E72 a): Mosbach ist genau einer PLZ zugeordnet → 74821 übernommen, Hinweis 'PLZ aus Ort ergänzt', Sitz-Genauigkeit plz_gebiet; Import ok</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="D19" s="24" t="inlineStr">
         <is>
-          <t>Nacharbeit; 'Meinten Sie …?' mit Kreis und Land; ähnlich zu Preview-Akteur 'Test: Kompostwerk Breisgau'</t>
+          <t>Nacharbeit (E72 b): Befund am Feld Sitz-PLZ nennt die Kandidaten mit Kreis und Land (Freiburg (Elbe), Landkreis Stade, Niedersachsen; Freiburg im Breisgau, Stadtkreis …, PLZ-Liste max. 10); nach Wahl der PLZ läuft der Akteur-Abgleich erneut → 'Test: Kompostwerk Breisgau' als stark-Vorschlag (E72 c)</t>
         </is>
       </c>
     </row>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="D37" s="24" t="inlineStr">
         <is>
-          <t>PLZ 68199 gehört zu Mannheim → 'Meinten Sie 68199 Mannheim?' oder Ortsteil-Toleranz (Weggabelung)</t>
+          <t>Ortsteil-Toleranz (E72 e): 'Mannheim-Neckarau' beginnt mit dem amtlichen Ort Mannheim + Trennzeichen → passt zu 68199, Ort bleibt unverändert, keine Meldung; Import ok ('Mannheimer Str.' wäre ein Befund)</t>
         </is>
       </c>
     </row>
